--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ОДЕСОС/РАЙОН ОДЕСОС.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ОДЕСОС/РАЙОН ОДЕСОС.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="32">
   <si>
     <t>Дата</t>
   </si>
@@ -53,12 +53,6 @@
   </si>
   <si>
     <t>Billing_Document</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>2026-05-12</t>
   </si>
   <si>
     <t>B8984BP</t>
@@ -122,8 +116,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -209,11 +204,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -221,9 +217,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -577,20 +573,20 @@
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" t="s">
-        <v>13</v>
+      <c r="A2" s="2">
+        <v>46149</v>
       </c>
       <c r="B2">
         <v>1148</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F2">
         <v>31.566</v>
@@ -608,7 +604,7 @@
         <v>26.2</v>
       </c>
       <c r="K2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -618,20 +614,20 @@
       </c>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" t="s">
-        <v>13</v>
+      <c r="A3" s="2">
+        <v>46149</v>
       </c>
       <c r="B3">
         <v>1148</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s">
         <v>19</v>
-      </c>
-      <c r="E3" t="s">
-        <v>21</v>
       </c>
       <c r="F3">
         <v>25.145</v>
@@ -649,7 +645,7 @@
         <v>20.87</v>
       </c>
       <c r="K3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -659,20 +655,20 @@
       </c>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" t="s">
-        <v>14</v>
+      <c r="A4" s="2">
+        <v>46154</v>
       </c>
       <c r="B4">
         <v>1148</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F4">
         <v>13.195</v>
@@ -690,7 +686,7 @@
         <v>10.82</v>
       </c>
       <c r="K4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -700,80 +696,80 @@
       </c>
     </row>
     <row r="7" spans="1:13">
-      <c r="A7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
+      <c r="A7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
     </row>
     <row r="8" spans="1:13">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="D8" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="E8" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="F8" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="G8" s="4" t="s">
         <v>30</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:13">
-      <c r="A9" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="5">
+      <c r="A9" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="6">
         <v>69.90600000000001</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9" s="6">
         <v>3</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="6">
         <v>0.8181</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="6">
         <v>57.19</v>
       </c>
-      <c r="F9" s="5">
+      <c r="F9" s="6">
         <v>57.89</v>
       </c>
-      <c r="G9" s="5">
+      <c r="G9" s="6">
         <v>0.7</v>
       </c>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10" s="7">
+      <c r="A10" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="8">
         <v>69.90600000000001</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="8">
         <v>3</v>
       </c>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7">
+      <c r="D10" s="8"/>
+      <c r="E10" s="8">
         <v>57.19</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="8">
         <v>57.89</v>
       </c>
-      <c r="G10" s="7">
+      <c r="G10" s="8">
         <v>0.7</v>
       </c>
     </row>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ОДЕСОС/РАЙОН ОДЕСОС.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ОДЕСОС/РАЙОН ОДЕСОС.xlsx
@@ -176,7 +176,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -186,12 +186,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -242,17 +236,17 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ОДЕСОС/РАЙОН ОДЕСОС.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ОДЕСОС/РАЙОН ОДЕСОС.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="25">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,79 +46,31 @@
     <t>Сума по ЕКО цена</t>
   </si>
   <si>
-    <t>Час</t>
-  </si>
-  <si>
     <t>Километри</t>
   </si>
   <si>
-    <t>Billing_Document</t>
-  </si>
-  <si>
-    <t>1148 Варна пристанище</t>
+    <t>Варна Порт</t>
+  </si>
+  <si>
+    <t>B0593BT</t>
+  </si>
+  <si>
+    <t>B8984BP</t>
   </si>
   <si>
     <t>B7235BP</t>
   </si>
   <si>
-    <t>B0593BT</t>
-  </si>
-  <si>
-    <t>B8984BP</t>
-  </si>
-  <si>
-    <t>B5779KH</t>
+    <t>78970155027722036</t>
+  </si>
+  <si>
+    <t>78970155027722051</t>
   </si>
   <si>
     <t>78970155027722044</t>
   </si>
   <si>
-    <t>78970155027722036</t>
-  </si>
-  <si>
-    <t>78970155027722051</t>
-  </si>
-  <si>
-    <t>78970155027722028</t>
-  </si>
-  <si>
-    <t>95 EKONOMY UNLEADED</t>
-  </si>
-  <si>
     <t>E GAS LPG</t>
-  </si>
-  <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>08:57:00</t>
-  </si>
-  <si>
-    <t>10:50:00</t>
-  </si>
-  <si>
-    <t>15:14:00</t>
-  </si>
-  <si>
-    <t>08:45:00</t>
-  </si>
-  <si>
-    <t>09:49:00</t>
-  </si>
-  <si>
-    <t>3232049379 3232049379</t>
-  </si>
-  <si>
-    <t>3232057219 3232057219</t>
-  </si>
-  <si>
-    <t>3232108153 3232108153</t>
-  </si>
-  <si>
-    <t>3232385384 3232385384</t>
-  </si>
-  <si>
-    <t>3232529015 3232529015</t>
   </si>
   <si>
     <t>Общи литри по продукт / РАЙОН ОДЕСОС</t>
@@ -541,7 +490,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -550,17 +499,14 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -594,239 +540,185 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="3">
+        <v>46174</v>
+      </c>
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="C2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2">
+        <v>23.68</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0.76</v>
+      </c>
+      <c r="H2">
+        <v>18</v>
+      </c>
+      <c r="I2" s="1">
+        <v>0.77</v>
+      </c>
+      <c r="J2">
+        <v>18.23</v>
+      </c>
+      <c r="K2">
+        <v>58385</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="3">
+        <v>46178</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="3">
-        <v>46160</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3">
+        <v>26.7</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0.73</v>
+      </c>
+      <c r="H3">
+        <v>19.49</v>
+      </c>
+      <c r="I3" s="1">
+        <v>0.74</v>
+      </c>
+      <c r="J3">
+        <v>19.76</v>
+      </c>
+      <c r="K3">
+        <v>64381</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="3">
+        <v>46182</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4">
+        <v>24.08</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0.71</v>
+      </c>
+      <c r="H4">
+        <v>17.1</v>
+      </c>
+      <c r="I4" s="1">
+        <v>0.72</v>
+      </c>
+      <c r="J4">
+        <v>17.34</v>
+      </c>
+      <c r="K4">
+        <v>58578</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="3">
+        <v>46185</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5">
+        <v>26.29</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="H5">
+        <v>17.61</v>
+      </c>
+      <c r="I5" s="1">
+        <v>0.68</v>
+      </c>
+      <c r="J5">
+        <v>17.88</v>
+      </c>
+      <c r="K5">
+        <v>64533</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="3">
+        <v>46185</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" t="s">
         <v>14</v>
       </c>
-      <c r="C2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="D6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6">
+        <v>26.07</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="H6">
+        <v>17.47</v>
+      </c>
+      <c r="I6" s="1">
+        <v>0.68</v>
+      </c>
+      <c r="J6">
+        <v>17.73</v>
+      </c>
+      <c r="K6">
+        <v>45480</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="4" t="s">
         <v>19</v>
-      </c>
-      <c r="E2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F2">
-        <v>10</v>
-      </c>
-      <c r="G2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H2">
-        <v>1.52</v>
-      </c>
-      <c r="I2" s="1">
-        <v>15.2</v>
-      </c>
-      <c r="J2">
-        <v>1.55</v>
-      </c>
-      <c r="K2" s="1">
-        <v>15.5</v>
-      </c>
-      <c r="L2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M2">
-        <v>45216</v>
-      </c>
-      <c r="N2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" s="3">
-        <v>46160</v>
-      </c>
-      <c r="B3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F3">
-        <v>12.8</v>
-      </c>
-      <c r="G3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H3">
-        <v>0.78</v>
-      </c>
-      <c r="I3" s="1">
-        <v>9.98</v>
-      </c>
-      <c r="J3">
-        <v>0.79</v>
-      </c>
-      <c r="K3" s="1">
-        <v>10.11</v>
-      </c>
-      <c r="L3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M3">
-        <v>58218</v>
-      </c>
-      <c r="N3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" s="3">
-        <v>46161</v>
-      </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F4">
-        <v>27.63</v>
-      </c>
-      <c r="G4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H4">
-        <v>0.78</v>
-      </c>
-      <c r="I4" s="1">
-        <v>21.55</v>
-      </c>
-      <c r="J4">
-        <v>0.79</v>
-      </c>
-      <c r="K4" s="1">
-        <v>21.83</v>
-      </c>
-      <c r="L4" t="s">
-        <v>28</v>
-      </c>
-      <c r="M4">
-        <v>64167</v>
-      </c>
-      <c r="N4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" s="3">
-        <v>46168</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5">
-        <v>19.77</v>
-      </c>
-      <c r="G5" t="s">
-        <v>25</v>
-      </c>
-      <c r="H5">
-        <v>0.78</v>
-      </c>
-      <c r="I5" s="1">
-        <v>15.42</v>
-      </c>
-      <c r="J5">
-        <v>0.79</v>
-      </c>
-      <c r="K5" s="1">
-        <v>15.62</v>
-      </c>
-      <c r="L5" t="s">
-        <v>29</v>
-      </c>
-      <c r="M5">
-        <v>45306</v>
-      </c>
-      <c r="N5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="3">
-        <v>46170</v>
-      </c>
-      <c r="B6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6">
-        <v>39.43</v>
-      </c>
-      <c r="G6" t="s">
-        <v>25</v>
-      </c>
-      <c r="H6">
-        <v>1.54</v>
-      </c>
-      <c r="I6" s="1">
-        <v>60.72</v>
-      </c>
-      <c r="J6">
-        <v>1.57</v>
-      </c>
-      <c r="K6" s="1">
-        <v>61.91</v>
-      </c>
-      <c r="L6" t="s">
-        <v>30</v>
-      </c>
-      <c r="M6">
-        <v>214982</v>
-      </c>
-      <c r="N6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="4" t="s">
-        <v>36</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -834,82 +726,62 @@
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:11">
       <c r="A10" s="5" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
       <c r="A11" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="7">
+        <v>126.82</v>
+      </c>
+      <c r="C11" s="7">
+        <v>5</v>
+      </c>
+      <c r="D11" s="8">
+        <v>0.7071</v>
+      </c>
+      <c r="E11" s="7">
+        <v>89.67</v>
+      </c>
+      <c r="F11" s="7">
+        <v>90.94</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="7">
-        <v>60.2</v>
-      </c>
-      <c r="C11" s="7">
-        <v>3</v>
-      </c>
-      <c r="D11" s="8">
-        <v>0.7799</v>
-      </c>
-      <c r="E11" s="7">
-        <v>46.95</v>
-      </c>
-      <c r="F11" s="7">
-        <v>47.56</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B12" s="7">
-        <v>49.43</v>
-      </c>
-      <c r="C12" s="7">
-        <v>2</v>
-      </c>
-      <c r="D12" s="8">
-        <v>1.5359</v>
-      </c>
-      <c r="E12" s="7">
-        <v>75.92</v>
-      </c>
-      <c r="F12" s="7">
-        <v>77.41</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="A13" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="B13" s="10">
-        <v>109.63</v>
-      </c>
-      <c r="C13" s="10">
+      <c r="B12" s="10">
+        <v>126.82</v>
+      </c>
+      <c r="C12" s="10">
         <v>5</v>
       </c>
-      <c r="D13" s="8"/>
-      <c r="E13" s="10">
-        <v>122.87</v>
-      </c>
-      <c r="F13" s="10">
-        <v>124.97</v>
+      <c r="D12" s="8"/>
+      <c r="E12" s="10">
+        <v>89.67</v>
+      </c>
+      <c r="F12" s="10">
+        <v>90.94</v>
       </c>
     </row>
   </sheetData>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ОДЕСОС/РАЙОН ОДЕСОС.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ОДЕСОС/РАЙОН ОДЕСОС.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="32">
   <si>
     <t>Дата</t>
   </si>
@@ -46,9 +46,15 @@
     <t>Сума по ЕКО цена</t>
   </si>
   <si>
+    <t>Час</t>
+  </si>
+  <si>
     <t>Километри</t>
   </si>
   <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>Варна Порт</t>
   </si>
   <si>
@@ -71,6 +77,21 @@
   </si>
   <si>
     <t>E GAS LPG</t>
+  </si>
+  <si>
+    <t>15:31</t>
+  </si>
+  <si>
+    <t>17:57</t>
+  </si>
+  <si>
+    <t>11:46</t>
+  </si>
+  <si>
+    <t>09:32</t>
+  </si>
+  <si>
+    <t>11:57</t>
   </si>
   <si>
     <t>Общи литри по продукт / РАЙОН ОДЕСОС</t>
@@ -490,7 +511,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -503,10 +524,12 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -540,22 +563,28 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="3">
         <v>46174</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F2">
         <v>23.68</v>
@@ -572,25 +601,31 @@
       <c r="J2">
         <v>18.23</v>
       </c>
-      <c r="K2">
+      <c r="K2" t="s">
+        <v>21</v>
+      </c>
+      <c r="L2">
         <v>58385</v>
       </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="M2">
+        <v>213586</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="3">
         <v>46178</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F3">
         <v>26.7</v>
@@ -607,25 +642,31 @@
       <c r="J3">
         <v>19.76</v>
       </c>
-      <c r="K3">
+      <c r="K3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L3">
         <v>64381</v>
       </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="M3">
+        <v>215389</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="3">
         <v>46182</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F4">
         <v>24.08</v>
@@ -642,25 +683,31 @@
       <c r="J4">
         <v>17.34</v>
       </c>
-      <c r="K4">
+      <c r="K4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L4">
         <v>58578</v>
       </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="M4">
+        <v>216735</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="3">
         <v>46185</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F5">
         <v>26.29</v>
@@ -677,25 +724,31 @@
       <c r="J5">
         <v>17.88</v>
       </c>
-      <c r="K5">
+      <c r="K5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5">
         <v>64533</v>
       </c>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="M5">
+        <v>218066</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="3">
         <v>46185</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F6">
         <v>26.07</v>
@@ -712,13 +765,19 @@
       <c r="J6">
         <v>17.73</v>
       </c>
-      <c r="K6">
+      <c r="K6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L6">
         <v>45480</v>
       </c>
-    </row>
-    <row r="9" spans="1:11">
+      <c r="M6">
+        <v>218174</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9" s="4" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -726,18 +785,18 @@
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:13">
       <c r="A10" s="5" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>7</v>
@@ -746,9 +805,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:13">
       <c r="A11" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B11" s="7">
         <v>126.82</v>
@@ -766,9 +825,9 @@
         <v>90.94</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:13">
       <c r="A12" s="9" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="B12" s="10">
         <v>126.82</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ОДЕСОС/РАЙОН ОДЕСОС.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ОДЕСОС/РАЙОН ОДЕСОС.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="28">
   <si>
     <t>Дата</t>
   </si>
@@ -49,49 +49,37 @@
     <t>Час</t>
   </si>
   <si>
-    <t>Километри</t>
-  </si>
-  <si>
-    <t>Billing_Document</t>
-  </si>
-  <si>
     <t>Варна Порт</t>
   </si>
   <si>
+    <t>B7235BP</t>
+  </si>
+  <si>
+    <t>B8984BP</t>
+  </si>
+  <si>
     <t>B0593BT</t>
   </si>
   <si>
-    <t>B8984BP</t>
-  </si>
-  <si>
-    <t>B7235BP</t>
+    <t>78970155027722044</t>
+  </si>
+  <si>
+    <t>78970155027722051</t>
   </si>
   <si>
     <t>78970155027722036</t>
   </si>
   <si>
-    <t>78970155027722051</t>
-  </si>
-  <si>
-    <t>78970155027722044</t>
-  </si>
-  <si>
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>15:31</t>
-  </si>
-  <si>
-    <t>17:57</t>
-  </si>
-  <si>
-    <t>11:46</t>
-  </si>
-  <si>
-    <t>09:32</t>
-  </si>
-  <si>
-    <t>11:57</t>
+    <t>2026-06-19 08:51:08</t>
+  </si>
+  <si>
+    <t>2026-06-19 11:40:11</t>
+  </si>
+  <si>
+    <t>2026-06-22 13:55:30</t>
   </si>
   <si>
     <t>Общи литри по продукт / РАЙОН ОДЕСОС</t>
@@ -511,7 +499,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -524,12 +512,10 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="21.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -563,101 +549,83 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="3">
+        <v>46192</v>
+      </c>
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="C2" t="s">
         <v>12</v>
       </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2">
+        <v>11.08</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="H2">
+        <v>7.2</v>
+      </c>
+      <c r="I2" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="J2">
+        <v>7.31</v>
+      </c>
+      <c r="K2" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="3">
-        <v>46174</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="3" spans="1:11">
+      <c r="A3" s="3">
+        <v>46192</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
         <v>13</v>
       </c>
-      <c r="C2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3">
+        <v>23.73</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="H3">
+        <v>15.42</v>
+      </c>
+      <c r="I3" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="J3">
+        <v>15.66</v>
+      </c>
+      <c r="K3" t="s">
         <v>20</v>
       </c>
-      <c r="F2">
-        <v>23.68</v>
-      </c>
-      <c r="G2" s="1">
-        <v>0.76</v>
-      </c>
-      <c r="H2">
-        <v>18</v>
-      </c>
-      <c r="I2" s="1">
-        <v>0.77</v>
-      </c>
-      <c r="J2">
-        <v>18.23</v>
-      </c>
-      <c r="K2" t="s">
-        <v>21</v>
-      </c>
-      <c r="L2">
-        <v>58385</v>
-      </c>
-      <c r="M2">
-        <v>213586</v>
-      </c>
     </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="3">
-        <v>46178</v>
-      </c>
-      <c r="B3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3">
-        <v>26.7</v>
-      </c>
-      <c r="G3" s="1">
-        <v>0.73</v>
-      </c>
-      <c r="H3">
-        <v>19.49</v>
-      </c>
-      <c r="I3" s="1">
-        <v>0.74</v>
-      </c>
-      <c r="J3">
-        <v>19.76</v>
-      </c>
-      <c r="K3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L3">
-        <v>64381</v>
-      </c>
-      <c r="M3">
-        <v>215389</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:11">
       <c r="A4" s="3">
-        <v>46182</v>
+        <v>46195</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
         <v>14</v>
@@ -666,186 +634,98 @@
         <v>17</v>
       </c>
       <c r="E4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F4">
-        <v>24.08</v>
+        <v>11.42</v>
       </c>
       <c r="G4" s="1">
-        <v>0.71</v>
+        <v>0.65</v>
       </c>
       <c r="H4">
-        <v>17.1</v>
+        <v>7.42</v>
       </c>
       <c r="I4" s="1">
-        <v>0.72</v>
+        <v>0.66</v>
       </c>
       <c r="J4">
-        <v>17.34</v>
+        <v>7.54</v>
       </c>
       <c r="K4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="L4">
-        <v>58578</v>
-      </c>
-      <c r="M4">
-        <v>216735</v>
+      <c r="B8" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="3">
-        <v>46185</v>
-      </c>
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" t="s">
+    <row r="9" spans="1:11">
+      <c r="A9" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5">
-        <v>26.29</v>
-      </c>
-      <c r="G5" s="1">
-        <v>0.67</v>
-      </c>
-      <c r="H5">
-        <v>17.61</v>
-      </c>
-      <c r="I5" s="1">
-        <v>0.68</v>
-      </c>
-      <c r="J5">
-        <v>17.88</v>
-      </c>
-      <c r="K5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L5">
-        <v>64533</v>
-      </c>
-      <c r="M5">
-        <v>218066</v>
+      <c r="B9" s="7">
+        <v>46.23</v>
+      </c>
+      <c r="C9" s="7">
+        <v>3</v>
+      </c>
+      <c r="D9" s="8">
+        <v>0.6498</v>
+      </c>
+      <c r="E9" s="7">
+        <v>30.04</v>
+      </c>
+      <c r="F9" s="7">
+        <v>30.51</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="3">
-        <v>46185</v>
-      </c>
-      <c r="B6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6">
-        <v>26.07</v>
-      </c>
-      <c r="G6" s="1">
-        <v>0.67</v>
-      </c>
-      <c r="H6">
-        <v>17.47</v>
-      </c>
-      <c r="I6" s="1">
-        <v>0.68</v>
-      </c>
-      <c r="J6">
-        <v>17.73</v>
-      </c>
-      <c r="K6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L6">
-        <v>45480</v>
-      </c>
-      <c r="M6">
-        <v>218174</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="5" t="s">
+    <row r="10" spans="1:11">
+      <c r="A10" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="7">
-        <v>126.82</v>
-      </c>
-      <c r="C11" s="7">
-        <v>5</v>
-      </c>
-      <c r="D11" s="8">
-        <v>0.7071</v>
-      </c>
-      <c r="E11" s="7">
-        <v>89.67</v>
-      </c>
-      <c r="F11" s="7">
-        <v>90.94</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="A12" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" s="10">
-        <v>126.82</v>
-      </c>
-      <c r="C12" s="10">
-        <v>5</v>
-      </c>
-      <c r="D12" s="8"/>
-      <c r="E12" s="10">
-        <v>89.67</v>
-      </c>
-      <c r="F12" s="10">
-        <v>90.94</v>
+      <c r="B10" s="10">
+        <v>46.23</v>
+      </c>
+      <c r="C10" s="10">
+        <v>3</v>
+      </c>
+      <c r="D10" s="8"/>
+      <c r="E10" s="10">
+        <v>30.04</v>
+      </c>
+      <c r="F10" s="10">
+        <v>30.51</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ОДЕСОС/РАЙОН ОДЕСОС.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ОДЕСОС/РАЙОН ОДЕСОС.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="41">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,37 +52,73 @@
     <t>Час</t>
   </si>
   <si>
-    <t>Варна Порт</t>
+    <t>Километри</t>
+  </si>
+  <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
+    <t>1148 Варна пристанище</t>
+  </si>
+  <si>
+    <t>B8984BP</t>
   </si>
   <si>
     <t>B7235BP</t>
   </si>
   <si>
-    <t>B8984BP</t>
-  </si>
-  <si>
     <t>B0593BT</t>
   </si>
   <si>
+    <t>78970155027722051</t>
+  </si>
+  <si>
     <t>78970155027722044</t>
   </si>
   <si>
-    <t>78970155027722051</t>
-  </si>
-  <si>
     <t>78970155027722036</t>
   </si>
   <si>
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>2026-06-19 08:51:08</t>
-  </si>
-  <si>
-    <t>2026-06-19 11:40:11</t>
-  </si>
-  <si>
-    <t>2026-06-22 13:55:30</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>11:40:00</t>
+  </si>
+  <si>
+    <t>08:51:00</t>
+  </si>
+  <si>
+    <t>13:55:00</t>
+  </si>
+  <si>
+    <t>09:05:00</t>
+  </si>
+  <si>
+    <t>16:44:00</t>
+  </si>
+  <si>
+    <t>08:56:00</t>
+  </si>
+  <si>
+    <t>3233534044 3233534044</t>
+  </si>
+  <si>
+    <t>3233582762 3233582762</t>
+  </si>
+  <si>
+    <t>3233713798 3233713798</t>
+  </si>
+  <si>
+    <t>3233938012 3233938012</t>
+  </si>
+  <si>
+    <t>3233948610 3233948610</t>
+  </si>
+  <si>
+    <t>3234097275 3234097275</t>
   </si>
   <si>
     <t>Общи литри по продукт / РАЙОН ОДЕСОС</t>
@@ -499,7 +538,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -508,14 +547,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -549,183 +591,351 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
         <v>46192</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F2">
-        <v>11.08</v>
-      </c>
-      <c r="G2" s="1">
+        <v>23.73</v>
+      </c>
+      <c r="G2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2">
         <v>0.65</v>
       </c>
-      <c r="H2">
-        <v>7.2</v>
-      </c>
       <c r="I2" s="1">
+        <v>15.42</v>
+      </c>
+      <c r="J2">
         <v>0.66</v>
       </c>
-      <c r="J2">
-        <v>7.31</v>
-      </c>
-      <c r="K2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="K2" s="1">
+        <v>15.66</v>
+      </c>
+      <c r="L2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M2">
+        <v>64720</v>
+      </c>
+      <c r="N2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="3">
         <v>46192</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F3">
-        <v>23.73</v>
-      </c>
-      <c r="G3" s="1">
+        <v>11.08</v>
+      </c>
+      <c r="G3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3">
         <v>0.65</v>
       </c>
-      <c r="H3">
-        <v>15.42</v>
-      </c>
       <c r="I3" s="1">
+        <v>7.2</v>
+      </c>
+      <c r="J3">
         <v>0.66</v>
       </c>
-      <c r="J3">
-        <v>15.66</v>
-      </c>
-      <c r="K3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="K3" s="1">
+        <v>7.31</v>
+      </c>
+      <c r="L3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M3">
+        <v>45549</v>
+      </c>
+      <c r="N3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="3">
         <v>46195</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F4">
         <v>11.42</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4">
         <v>0.65</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>7.42</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>0.66</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>7.54</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
+        <v>25</v>
+      </c>
+      <c r="M4">
+        <v>58778</v>
+      </c>
+      <c r="N4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" s="3">
+        <v>46199</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7" s="4" t="s">
+      <c r="F5">
+        <v>23.53</v>
+      </c>
+      <c r="G5" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="A8" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="5" t="s">
+      <c r="H5">
+        <v>0.65</v>
+      </c>
+      <c r="I5" s="1">
+        <v>15.29</v>
+      </c>
+      <c r="J5">
+        <v>0.66</v>
+      </c>
+      <c r="K5" s="1">
+        <v>15.53</v>
+      </c>
+      <c r="L5" t="s">
         <v>26</v>
       </c>
-      <c r="E8" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="A9" s="6" t="s">
+      <c r="M5">
+        <v>58815</v>
+      </c>
+      <c r="N5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" s="3">
+        <v>46199</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="7">
-        <v>46.23</v>
-      </c>
-      <c r="C9" s="7">
-        <v>3</v>
-      </c>
-      <c r="D9" s="8">
-        <v>0.6498</v>
-      </c>
-      <c r="E9" s="7">
-        <v>30.04</v>
-      </c>
-      <c r="F9" s="7">
-        <v>30.51</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="A10" s="9" t="s">
+      <c r="E6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6">
+        <v>25.83</v>
+      </c>
+      <c r="G6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H6">
+        <v>0.65</v>
+      </c>
+      <c r="I6" s="1">
+        <v>16.79</v>
+      </c>
+      <c r="J6">
+        <v>0.66</v>
+      </c>
+      <c r="K6" s="1">
+        <v>17.05</v>
+      </c>
+      <c r="L6" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="10">
-        <v>46.23</v>
-      </c>
-      <c r="C10" s="10">
-        <v>3</v>
-      </c>
-      <c r="D10" s="8"/>
-      <c r="E10" s="10">
-        <v>30.04</v>
-      </c>
-      <c r="F10" s="10">
-        <v>30.51</v>
+      <c r="M6">
+        <v>64894</v>
+      </c>
+      <c r="N6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" s="3">
+        <v>46203</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7">
+        <v>22.77</v>
+      </c>
+      <c r="G7" t="s">
+        <v>22</v>
+      </c>
+      <c r="H7">
+        <v>0.65</v>
+      </c>
+      <c r="I7" s="1">
+        <v>14.8</v>
+      </c>
+      <c r="J7">
+        <v>0.66</v>
+      </c>
+      <c r="K7" s="1">
+        <v>15.03</v>
+      </c>
+      <c r="L7" t="s">
+        <v>28</v>
+      </c>
+      <c r="M7">
+        <v>65022</v>
+      </c>
+      <c r="N7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="7">
+        <v>118.36</v>
+      </c>
+      <c r="C12" s="7">
+        <v>6</v>
+      </c>
+      <c r="D12" s="8">
+        <v>0.6499</v>
+      </c>
+      <c r="E12" s="7">
+        <v>76.92</v>
+      </c>
+      <c r="F12" s="7">
+        <v>78.12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="10">
+        <v>118.36</v>
+      </c>
+      <c r="C13" s="10">
+        <v>6</v>
+      </c>
+      <c r="D13" s="8"/>
+      <c r="E13" s="10">
+        <v>76.92</v>
+      </c>
+      <c r="F13" s="10">
+        <v>78.12</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A10:F10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ОДЕСОС/РАЙОН ОДЕСОС.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ОДЕСОС/РАЙОН ОДЕСОС.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="33">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -58,67 +55,46 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>1148 Варна пристанище</t>
+    <t>Варна Порт</t>
+  </si>
+  <si>
+    <t>B7235BP</t>
   </si>
   <si>
     <t>B8984BP</t>
   </si>
   <si>
-    <t>B7235BP</t>
-  </si>
-  <si>
     <t>B0593BT</t>
   </si>
   <si>
+    <t>78970155027722044</t>
+  </si>
+  <si>
     <t>78970155027722051</t>
   </si>
   <si>
-    <t>78970155027722044</t>
-  </si>
-  <si>
     <t>78970155027722036</t>
   </si>
   <si>
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>11:40:00</t>
-  </si>
-  <si>
-    <t>08:51:00</t>
-  </si>
-  <si>
-    <t>13:55:00</t>
-  </si>
-  <si>
-    <t>09:05:00</t>
-  </si>
-  <si>
-    <t>16:44:00</t>
-  </si>
-  <si>
-    <t>08:56:00</t>
-  </si>
-  <si>
-    <t>3233534044 3233534044</t>
-  </si>
-  <si>
-    <t>3233582762 3233582762</t>
-  </si>
-  <si>
-    <t>3233713798 3233713798</t>
-  </si>
-  <si>
-    <t>3233938012 3233938012</t>
-  </si>
-  <si>
-    <t>3233948610 3233948610</t>
-  </si>
-  <si>
-    <t>3234097275 3234097275</t>
+    <t>08:52</t>
+  </si>
+  <si>
+    <t>11:41</t>
+  </si>
+  <si>
+    <t>13:56</t>
+  </si>
+  <si>
+    <t>09:05</t>
+  </si>
+  <si>
+    <t>16:44</t>
+  </si>
+  <si>
+    <t>08:56</t>
   </si>
   <si>
     <t>Общи литри по продукт / РАЙОН ОДЕСОС</t>
@@ -538,7 +514,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -547,17 +523,16 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -597,192 +572,177 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="3">
         <v>46192</v>
       </c>
       <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
         <v>14</v>
       </c>
-      <c r="C2" t="s">
-        <v>15</v>
-      </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2">
+        <v>11.08</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="H2">
+        <v>7.2</v>
+      </c>
+      <c r="I2" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="J2">
+        <v>7.31</v>
+      </c>
+      <c r="K2" t="s">
         <v>21</v>
       </c>
-      <c r="F2">
-        <v>23.73</v>
-      </c>
-      <c r="G2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H2">
-        <v>0.65</v>
-      </c>
-      <c r="I2" s="1">
-        <v>15.42</v>
-      </c>
-      <c r="J2">
-        <v>0.66</v>
-      </c>
-      <c r="K2" s="1">
-        <v>15.66</v>
-      </c>
-      <c r="L2" t="s">
-        <v>23</v>
+      <c r="L2">
+        <v>45549</v>
       </c>
       <c r="M2">
-        <v>64720</v>
-      </c>
-      <c r="N2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+        <v>221078</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="3">
         <v>46192</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F3">
-        <v>11.08</v>
-      </c>
-      <c r="G3" t="s">
+        <v>23.73</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="H3">
+        <v>15.42</v>
+      </c>
+      <c r="I3" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="J3">
+        <v>15.66</v>
+      </c>
+      <c r="K3" t="s">
         <v>22</v>
       </c>
-      <c r="H3">
-        <v>0.65</v>
-      </c>
-      <c r="I3" s="1">
-        <v>7.2</v>
-      </c>
-      <c r="J3">
-        <v>0.66</v>
-      </c>
-      <c r="K3" s="1">
-        <v>7.31</v>
-      </c>
-      <c r="L3" t="s">
-        <v>24</v>
+      <c r="L3">
+        <v>64720</v>
       </c>
       <c r="M3">
-        <v>45549</v>
-      </c>
-      <c r="N3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+        <v>221194</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="3">
         <v>46195</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" t="s">
         <v>20</v>
-      </c>
-      <c r="E4" t="s">
-        <v>21</v>
       </c>
       <c r="F4">
         <v>11.42</v>
       </c>
-      <c r="G4" t="s">
-        <v>22</v>
+      <c r="G4" s="1">
+        <v>0.65</v>
       </c>
       <c r="H4">
-        <v>0.65</v>
+        <v>7.42</v>
       </c>
       <c r="I4" s="1">
-        <v>7.42</v>
+        <v>0.66</v>
       </c>
       <c r="J4">
-        <v>0.66</v>
-      </c>
-      <c r="K4" s="1">
         <v>7.54</v>
       </c>
-      <c r="L4" t="s">
-        <v>25</v>
+      <c r="K4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L4">
+        <v>58778</v>
       </c>
       <c r="M4">
-        <v>58778</v>
-      </c>
-      <c r="N4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+        <v>222460</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="3">
         <v>46199</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" t="s">
         <v>20</v>
-      </c>
-      <c r="E5" t="s">
-        <v>21</v>
       </c>
       <c r="F5">
         <v>23.53</v>
       </c>
-      <c r="G5" t="s">
-        <v>22</v>
+      <c r="G5" s="1">
+        <v>0.65</v>
       </c>
       <c r="H5">
-        <v>0.65</v>
+        <v>15.29</v>
       </c>
       <c r="I5" s="1">
-        <v>15.29</v>
+        <v>0.66</v>
       </c>
       <c r="J5">
-        <v>0.66</v>
-      </c>
-      <c r="K5" s="1">
         <v>15.53</v>
       </c>
-      <c r="L5" t="s">
-        <v>26</v>
+      <c r="K5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5">
+        <v>58815</v>
       </c>
       <c r="M5">
-        <v>58815</v>
-      </c>
-      <c r="N5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+        <v>224233</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="3">
         <v>46199</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
         <v>15</v>
@@ -791,42 +751,39 @@
         <v>18</v>
       </c>
       <c r="E6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F6">
         <v>25.83</v>
       </c>
-      <c r="G6" t="s">
-        <v>22</v>
+      <c r="G6" s="1">
+        <v>0.65</v>
       </c>
       <c r="H6">
-        <v>0.65</v>
+        <v>16.79</v>
       </c>
       <c r="I6" s="1">
-        <v>16.79</v>
+        <v>0.66</v>
       </c>
       <c r="J6">
-        <v>0.66</v>
-      </c>
-      <c r="K6" s="1">
         <v>17.05</v>
       </c>
-      <c r="L6" t="s">
-        <v>27</v>
+      <c r="K6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L6">
+        <v>64894</v>
       </c>
       <c r="M6">
-        <v>64894</v>
-      </c>
-      <c r="N6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+        <v>224591</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" s="3">
         <v>46203</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
         <v>15</v>
@@ -835,39 +792,36 @@
         <v>18</v>
       </c>
       <c r="E7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F7">
         <v>22.77</v>
       </c>
-      <c r="G7" t="s">
-        <v>22</v>
+      <c r="G7" s="1">
+        <v>0.65</v>
       </c>
       <c r="H7">
-        <v>0.65</v>
+        <v>14.8</v>
       </c>
       <c r="I7" s="1">
-        <v>14.8</v>
+        <v>0.66</v>
       </c>
       <c r="J7">
-        <v>0.66</v>
-      </c>
-      <c r="K7" s="1">
         <v>15.03</v>
       </c>
-      <c r="L7" t="s">
-        <v>28</v>
+      <c r="K7" t="s">
+        <v>26</v>
+      </c>
+      <c r="L7">
+        <v>65022</v>
       </c>
       <c r="M7">
-        <v>65022</v>
-      </c>
-      <c r="N7" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+        <v>225796</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10" s="4" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -875,29 +829,29 @@
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:13">
       <c r="A11" s="5" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
       <c r="A12" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B12" s="7">
         <v>118.36</v>
@@ -915,9 +869,9 @@
         <v>78.12</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:13">
       <c r="A13" s="9" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="B13" s="10">
         <v>118.36</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ОДЕСОС/РАЙОН ОДЕСОС.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ОДЕСОС/РАЙОН ОДЕСОС.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="41">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -52,37 +55,70 @@
     <t>Километри</t>
   </si>
   <si>
-    <t>Варна Порт</t>
+    <t>Billing_Document</t>
+  </si>
+  <si>
+    <t>1148 Варна пристанище</t>
+  </si>
+  <si>
+    <t>B0593BT</t>
+  </si>
+  <si>
+    <t>B8984BP</t>
   </si>
   <si>
     <t>B7235BP</t>
   </si>
   <si>
-    <t>B0593BT</t>
-  </si>
-  <si>
-    <t>B8984BP</t>
+    <t>78970155027722036</t>
+  </si>
+  <si>
+    <t>78970155027722051</t>
   </si>
   <si>
     <t>78970155027722044</t>
   </si>
   <si>
-    <t>78970155027722036</t>
-  </si>
-  <si>
-    <t>78970155027722051</t>
-  </si>
-  <si>
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>2026-07-01 12:09:19</t>
-  </si>
-  <si>
-    <t>2026-07-07 11:48:10</t>
-  </si>
-  <si>
-    <t>2026-07-09 10:06:40</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>11:35:00</t>
+  </si>
+  <si>
+    <t>14:37:00</t>
+  </si>
+  <si>
+    <t>14:24:00</t>
+  </si>
+  <si>
+    <t>12:23:00</t>
+  </si>
+  <si>
+    <t>11:55:00</t>
+  </si>
+  <si>
+    <t>08:50:00</t>
+  </si>
+  <si>
+    <t>3234890709 3234890709</t>
+  </si>
+  <si>
+    <t>3234895410 3234895410</t>
+  </si>
+  <si>
+    <t>3235101624 3235101624</t>
+  </si>
+  <si>
+    <t>3235242300 3235242300</t>
+  </si>
+  <si>
+    <t>3235298516 3235298516</t>
+  </si>
+  <si>
+    <t>3235580631 3235580631</t>
   </si>
   <si>
     <t>Общи литри по продукт / РАЙОН ОДЕСОС</t>
@@ -502,7 +538,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -511,15 +547,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -556,192 +594,348 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
-        <v>46204</v>
+        <v>46219</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2">
+        <v>20.71</v>
+      </c>
+      <c r="G2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2">
+        <v>0.62</v>
+      </c>
+      <c r="I2" s="1">
+        <v>12.84</v>
+      </c>
+      <c r="J2">
+        <v>0.63</v>
+      </c>
+      <c r="K2" s="1">
+        <v>13.05</v>
+      </c>
+      <c r="L2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M2">
+        <v>59128</v>
+      </c>
+      <c r="N2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="3">
+        <v>46219</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
         <v>16</v>
       </c>
-      <c r="E2" t="s">
+      <c r="D3" t="s">
         <v>19</v>
       </c>
-      <c r="F2">
-        <v>26.08</v>
-      </c>
-      <c r="G2" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="H2">
-        <v>16.95</v>
-      </c>
-      <c r="I2" s="1">
-        <v>0.66</v>
-      </c>
-      <c r="J2">
-        <v>17.21</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3">
+        <v>28.13</v>
+      </c>
+      <c r="G3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3">
+        <v>0.62</v>
+      </c>
+      <c r="I3" s="1">
+        <v>17.44</v>
+      </c>
+      <c r="J3">
+        <v>0.63</v>
+      </c>
+      <c r="K3" s="1">
+        <v>17.72</v>
+      </c>
+      <c r="L3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M3">
+        <v>65338</v>
+      </c>
+      <c r="N3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" s="3">
+        <v>46223</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
         <v>20</v>
       </c>
-      <c r="L2">
-        <v>457011</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="3">
-        <v>46210</v>
-      </c>
-      <c r="B3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="E4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4">
+        <v>25.95</v>
+      </c>
+      <c r="G4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4">
+        <v>0.63</v>
+      </c>
+      <c r="I4" s="1">
+        <v>16.35</v>
+      </c>
+      <c r="J4">
+        <v>0.64</v>
+      </c>
+      <c r="K4" s="1">
+        <v>16.61</v>
+      </c>
+      <c r="L4" t="s">
+        <v>25</v>
+      </c>
+      <c r="M4">
+        <v>862</v>
+      </c>
+      <c r="N4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" s="3">
+        <v>46226</v>
+      </c>
+      <c r="B5" t="s">
         <v>14</v>
       </c>
-      <c r="D3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="C5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" t="s">
         <v>19</v>
       </c>
-      <c r="F3">
-        <v>28.49</v>
-      </c>
-      <c r="G3" s="1">
-        <v>0.62</v>
-      </c>
-      <c r="H3">
-        <v>17.66</v>
-      </c>
-      <c r="I3" s="1">
+      <c r="E5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5">
+        <v>25.59</v>
+      </c>
+      <c r="G5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H5">
         <v>0.63</v>
       </c>
-      <c r="J3">
-        <v>17.95</v>
-      </c>
-      <c r="K3" t="s">
+      <c r="I5" s="1">
+        <v>16.12</v>
+      </c>
+      <c r="J5">
+        <v>0.64</v>
+      </c>
+      <c r="K5" s="1">
+        <v>16.38</v>
+      </c>
+      <c r="L5" t="s">
+        <v>26</v>
+      </c>
+      <c r="M5">
+        <v>65471</v>
+      </c>
+      <c r="N5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" s="3">
+        <v>46227</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" t="s">
         <v>21</v>
       </c>
-      <c r="L3">
-        <v>58992</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="3">
-        <v>46212</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="F6">
+        <v>20.59</v>
+      </c>
+      <c r="G6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H6">
+        <v>0.63</v>
+      </c>
+      <c r="I6" s="1">
+        <v>12.97</v>
+      </c>
+      <c r="J6">
+        <v>0.64</v>
+      </c>
+      <c r="K6" s="1">
+        <v>13.18</v>
+      </c>
+      <c r="L6" t="s">
+        <v>27</v>
+      </c>
+      <c r="M6">
+        <v>59270</v>
+      </c>
+      <c r="N6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" s="3">
+        <v>46233</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" t="s">
         <v>19</v>
       </c>
-      <c r="F4">
-        <v>31.48</v>
-      </c>
-      <c r="G4" s="1">
-        <v>0.62</v>
-      </c>
-      <c r="H4">
-        <v>19.52</v>
-      </c>
-      <c r="I4" s="1">
+      <c r="E7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7">
+        <v>23.36</v>
+      </c>
+      <c r="G7" t="s">
+        <v>22</v>
+      </c>
+      <c r="H7">
         <v>0.63</v>
       </c>
-      <c r="J4">
-        <v>19.83</v>
-      </c>
-      <c r="K4" t="s">
-        <v>22</v>
-      </c>
-      <c r="L4">
-        <v>65188</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="A9" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="7">
-        <v>86.05</v>
-      </c>
-      <c r="C9" s="7">
-        <v>3</v>
-      </c>
-      <c r="D9" s="8">
-        <v>0.6291</v>
-      </c>
-      <c r="E9" s="7">
-        <v>54.13</v>
-      </c>
-      <c r="F9" s="7">
-        <v>54.99</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
-      <c r="A10" s="9" t="s">
+      <c r="I7" s="1">
+        <v>14.72</v>
+      </c>
+      <c r="J7">
+        <v>0.64</v>
+      </c>
+      <c r="K7" s="1">
+        <v>14.95</v>
+      </c>
+      <c r="L7" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="10">
-        <v>86.05</v>
-      </c>
-      <c r="C10" s="10">
-        <v>3</v>
-      </c>
-      <c r="D10" s="8"/>
-      <c r="E10" s="10">
-        <v>54.13</v>
-      </c>
-      <c r="F10" s="10">
-        <v>54.99</v>
+      <c r="M7">
+        <v>65636</v>
+      </c>
+      <c r="N7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="7">
+        <v>144.33</v>
+      </c>
+      <c r="C12" s="7">
+        <v>6</v>
+      </c>
+      <c r="D12" s="8">
+        <v>0.6266</v>
+      </c>
+      <c r="E12" s="7">
+        <v>90.44</v>
+      </c>
+      <c r="F12" s="7">
+        <v>91.89</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="10">
+        <v>144.33</v>
+      </c>
+      <c r="C13" s="10">
+        <v>6</v>
+      </c>
+      <c r="D13" s="8"/>
+      <c r="E13" s="10">
+        <v>90.44</v>
+      </c>
+      <c r="F13" s="10">
+        <v>91.89</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A10:F10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ОДЕСОС/РАЙОН ОДЕСОС.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ОДЕСОС/РАЙОН ОДЕСОС.xlsx
@@ -146,7 +146,7 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -906,7 +906,7 @@
         <v>6</v>
       </c>
       <c r="D12" s="8">
-        <v>0.6266</v>
+        <v>0.62662</v>
       </c>
       <c r="E12" s="7">
         <v>90.44</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ОДЕСОС/РАЙОН ОДЕСОС.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ОДЕСОС/РАЙОН ОДЕСОС.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="42">
   <si>
     <t>Дата</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>Тип количество</t>
+  </si>
+  <si>
+    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -538,7 +541,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -551,13 +554,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -600,274 +603,295 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" s="3">
         <v>46219</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F2">
-        <v>20.71</v>
+        <v>20.714</v>
       </c>
       <c r="G2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2" s="1">
         <v>0.62</v>
       </c>
-      <c r="I2" s="1">
-        <v>12.84</v>
-      </c>
       <c r="J2">
+        <v>12.84268</v>
+      </c>
+      <c r="K2" s="1">
         <v>0.63</v>
       </c>
-      <c r="K2" s="1">
-        <v>13.05</v>
-      </c>
-      <c r="L2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M2">
+      <c r="L2" s="1">
+        <v>13.04982</v>
+      </c>
+      <c r="M2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N2">
         <v>59128</v>
       </c>
-      <c r="N2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+      <c r="O2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" s="3">
         <v>46219</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F3">
-        <v>28.13</v>
+        <v>28.127</v>
       </c>
       <c r="G3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3" s="1">
         <v>0.62</v>
       </c>
-      <c r="I3" s="1">
-        <v>17.44</v>
-      </c>
       <c r="J3">
+        <v>17.43874</v>
+      </c>
+      <c r="K3" s="1">
         <v>0.63</v>
       </c>
-      <c r="K3" s="1">
-        <v>17.72</v>
-      </c>
-      <c r="L3" t="s">
-        <v>24</v>
-      </c>
-      <c r="M3">
+      <c r="L3" s="1">
+        <v>17.72001</v>
+      </c>
+      <c r="M3" t="s">
+        <v>25</v>
+      </c>
+      <c r="N3">
         <v>65338</v>
       </c>
-      <c r="N3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+      <c r="O3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" s="3">
         <v>46223</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F4">
-        <v>25.95</v>
+        <v>25.953</v>
       </c>
       <c r="G4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4" s="1">
         <v>0.63</v>
       </c>
-      <c r="I4" s="1">
-        <v>16.35</v>
-      </c>
       <c r="J4">
+        <v>16.35039</v>
+      </c>
+      <c r="K4" s="1">
         <v>0.64</v>
       </c>
-      <c r="K4" s="1">
-        <v>16.61</v>
-      </c>
-      <c r="L4" t="s">
-        <v>25</v>
-      </c>
-      <c r="M4">
+      <c r="L4" s="1">
+        <v>16.60992</v>
+      </c>
+      <c r="M4" t="s">
+        <v>26</v>
+      </c>
+      <c r="N4">
         <v>862</v>
       </c>
-      <c r="N4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+      <c r="O4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5" s="3">
         <v>46226</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F5">
-        <v>25.59</v>
+        <v>25.594</v>
       </c>
       <c r="G5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5" s="1">
         <v>0.63</v>
       </c>
-      <c r="I5" s="1">
-        <v>16.12</v>
-      </c>
       <c r="J5">
+        <v>16.12422</v>
+      </c>
+      <c r="K5" s="1">
         <v>0.64</v>
       </c>
-      <c r="K5" s="1">
-        <v>16.38</v>
-      </c>
-      <c r="L5" t="s">
-        <v>26</v>
-      </c>
-      <c r="M5">
+      <c r="L5" s="1">
+        <v>16.38016</v>
+      </c>
+      <c r="M5" t="s">
+        <v>27</v>
+      </c>
+      <c r="N5">
         <v>65471</v>
       </c>
-      <c r="N5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+      <c r="O5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6" s="3">
         <v>46227</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F6">
-        <v>20.59</v>
+        <v>20.594</v>
       </c>
       <c r="G6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6" s="1">
         <v>0.63</v>
       </c>
-      <c r="I6" s="1">
-        <v>12.97</v>
-      </c>
       <c r="J6">
+        <v>12.97422</v>
+      </c>
+      <c r="K6" s="1">
         <v>0.64</v>
       </c>
-      <c r="K6" s="1">
-        <v>13.18</v>
-      </c>
-      <c r="L6" t="s">
-        <v>27</v>
-      </c>
-      <c r="M6">
+      <c r="L6" s="1">
+        <v>13.18016</v>
+      </c>
+      <c r="M6" t="s">
+        <v>28</v>
+      </c>
+      <c r="N6">
         <v>59270</v>
       </c>
-      <c r="N6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+      <c r="O6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7" s="3">
         <v>46233</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F7">
-        <v>23.36</v>
+        <v>23.359</v>
       </c>
       <c r="G7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7" s="1">
         <v>0.63</v>
       </c>
-      <c r="I7" s="1">
-        <v>14.72</v>
-      </c>
       <c r="J7">
+        <v>14.71617</v>
+      </c>
+      <c r="K7" s="1">
         <v>0.64</v>
       </c>
-      <c r="K7" s="1">
-        <v>14.95</v>
-      </c>
-      <c r="L7" t="s">
-        <v>28</v>
-      </c>
-      <c r="M7">
+      <c r="L7" s="1">
+        <v>14.94976</v>
+      </c>
+      <c r="M7" t="s">
+        <v>29</v>
+      </c>
+      <c r="N7">
         <v>65636</v>
       </c>
-      <c r="N7" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+      <c r="O7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
       <c r="A10" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -875,59 +899,59 @@
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:15">
       <c r="A11" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
       <c r="A12" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" s="7">
-        <v>144.33</v>
+        <v>144.341</v>
       </c>
       <c r="C12" s="7">
         <v>6</v>
       </c>
       <c r="D12" s="8">
-        <v>0.62662</v>
+        <v>0.626616</v>
       </c>
       <c r="E12" s="7">
-        <v>90.44</v>
+        <v>90.45</v>
       </c>
       <c r="F12" s="7">
         <v>91.89</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:15">
       <c r="A13" s="9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B13" s="10">
-        <v>144.33</v>
+        <v>144.341</v>
       </c>
       <c r="C13" s="10">
         <v>6</v>
       </c>
       <c r="D13" s="8"/>
       <c r="E13" s="10">
-        <v>90.44</v>
+        <v>90.45</v>
       </c>
       <c r="F13" s="10">
         <v>91.89</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ОДЕСОС/РАЙОН ОДЕСОС.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ОДЕСОС/РАЙОН ОДЕСОС.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="41">
   <si>
     <t>Дата</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Тип количество</t>
-  </si>
-  <si>
-    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -147,9 +144,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -243,10 +240,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -541,7 +538,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -554,13 +551,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -603,295 +600,274 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15">
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
         <v>46219</v>
       </c>
       <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
         <v>15</v>
       </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
       <c r="D2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F2">
         <v>20.714</v>
       </c>
       <c r="G2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2">
+        <v>0.62</v>
+      </c>
+      <c r="I2" s="1">
+        <v>12.843</v>
+      </c>
+      <c r="J2">
+        <v>0.63</v>
+      </c>
+      <c r="K2" s="1">
+        <v>13.05</v>
+      </c>
+      <c r="L2" t="s">
         <v>23</v>
       </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2" s="1">
-        <v>0.62</v>
-      </c>
-      <c r="J2">
-        <v>12.84268</v>
-      </c>
-      <c r="K2" s="1">
-        <v>0.63</v>
-      </c>
-      <c r="L2" s="1">
-        <v>13.04982</v>
-      </c>
-      <c r="M2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N2">
+      <c r="M2">
         <v>59128</v>
       </c>
-      <c r="O2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+      <c r="N2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="3">
         <v>46219</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F3">
         <v>28.127</v>
       </c>
       <c r="G3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>0.62</v>
       </c>
       <c r="I3" s="1">
-        <v>0.62</v>
+        <v>17.439</v>
       </c>
       <c r="J3">
-        <v>17.43874</v>
+        <v>0.63</v>
       </c>
       <c r="K3" s="1">
-        <v>0.63</v>
-      </c>
-      <c r="L3" s="1">
-        <v>17.72001</v>
-      </c>
-      <c r="M3" t="s">
-        <v>25</v>
-      </c>
-      <c r="N3">
+        <v>17.72</v>
+      </c>
+      <c r="L3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M3">
         <v>65338</v>
       </c>
-      <c r="O3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+      <c r="N3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="3">
         <v>46223</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
         <v>21</v>
-      </c>
-      <c r="E4" t="s">
-        <v>22</v>
       </c>
       <c r="F4">
         <v>25.953</v>
       </c>
       <c r="G4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I4" s="1">
-        <v>0.63</v>
+        <v>16.35</v>
       </c>
       <c r="J4">
-        <v>16.35039</v>
+        <v>0.64</v>
       </c>
       <c r="K4" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L4" s="1">
-        <v>16.60992</v>
-      </c>
-      <c r="M4" t="s">
-        <v>26</v>
-      </c>
-      <c r="N4">
+        <v>16.61</v>
+      </c>
+      <c r="L4" t="s">
+        <v>25</v>
+      </c>
+      <c r="M4">
         <v>862</v>
       </c>
-      <c r="O4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+      <c r="N4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="3">
         <v>46226</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F5">
         <v>25.594</v>
       </c>
       <c r="G5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I5" s="1">
-        <v>0.63</v>
+        <v>16.124</v>
       </c>
       <c r="J5">
-        <v>16.12422</v>
+        <v>0.64</v>
       </c>
       <c r="K5" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L5" s="1">
-        <v>16.38016</v>
-      </c>
-      <c r="M5" t="s">
-        <v>27</v>
-      </c>
-      <c r="N5">
+        <v>16.38</v>
+      </c>
+      <c r="L5" t="s">
+        <v>26</v>
+      </c>
+      <c r="M5">
         <v>65471</v>
       </c>
-      <c r="O5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+      <c r="N5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" s="3">
         <v>46227</v>
       </c>
       <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
         <v>15</v>
       </c>
-      <c r="C6" t="s">
-        <v>16</v>
-      </c>
       <c r="D6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F6">
         <v>20.594</v>
       </c>
       <c r="G6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I6" s="1">
-        <v>0.63</v>
+        <v>12.974</v>
       </c>
       <c r="J6">
-        <v>12.97422</v>
+        <v>0.64</v>
       </c>
       <c r="K6" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L6" s="1">
-        <v>13.18016</v>
-      </c>
-      <c r="M6" t="s">
-        <v>28</v>
-      </c>
-      <c r="N6">
+        <v>13.18</v>
+      </c>
+      <c r="L6" t="s">
+        <v>27</v>
+      </c>
+      <c r="M6">
         <v>59270</v>
       </c>
-      <c r="O6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+      <c r="N6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" s="3">
         <v>46233</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F7">
         <v>23.359</v>
       </c>
       <c r="G7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H7">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I7" s="1">
-        <v>0.63</v>
+        <v>14.716</v>
       </c>
       <c r="J7">
-        <v>14.71617</v>
+        <v>0.64</v>
       </c>
       <c r="K7" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L7" s="1">
-        <v>14.94976</v>
-      </c>
-      <c r="M7" t="s">
-        <v>29</v>
-      </c>
-      <c r="N7">
+        <v>14.95</v>
+      </c>
+      <c r="L7" t="s">
+        <v>28</v>
+      </c>
+      <c r="M7">
         <v>65636</v>
       </c>
-      <c r="O7" t="s">
+      <c r="N7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="4" t="s">
         <v>35</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
-      <c r="A10" s="4" t="s">
-        <v>36</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -899,49 +875,49 @@
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:14">
       <c r="A11" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="C11" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="D11" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="D11" s="5" t="s">
-        <v>40</v>
-      </c>
       <c r="E11" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B12" s="7">
         <v>144.341</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="8">
         <v>6</v>
       </c>
       <c r="D12" s="8">
-        <v>0.626616</v>
-      </c>
-      <c r="E12" s="7">
-        <v>90.45</v>
-      </c>
-      <c r="F12" s="7">
+        <v>0.627</v>
+      </c>
+      <c r="E12" s="8">
+        <v>90.446</v>
+      </c>
+      <c r="F12" s="8">
         <v>91.89</v>
       </c>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:14">
       <c r="A13" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B13" s="10">
         <v>144.341</v>
@@ -951,7 +927,7 @@
       </c>
       <c r="D13" s="8"/>
       <c r="E13" s="10">
-        <v>90.45</v>
+        <v>90.446</v>
       </c>
       <c r="F13" s="10">
         <v>91.89</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ОДЕСОС/РАЙОН ОДЕСОС.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ОДЕСОС/РАЙОН ОДЕСОС.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="36">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -58,67 +55,55 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>1148 Варна пристанище</t>
+    <t>Варна Порт</t>
+  </si>
+  <si>
+    <t>B7235BP</t>
   </si>
   <si>
     <t>B0593BT</t>
   </si>
   <si>
+    <t>B5779KH</t>
+  </si>
+  <si>
     <t>B8984BP</t>
   </si>
   <si>
-    <t>B7235BP</t>
+    <t>78970155027722044</t>
   </si>
   <si>
     <t>78970155027722036</t>
   </si>
   <si>
+    <t>78970155027722028</t>
+  </si>
+  <si>
     <t>78970155027722051</t>
   </si>
   <si>
-    <t>78970155027722044</t>
-  </si>
-  <si>
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>11:35:00</t>
-  </si>
-  <si>
-    <t>14:37:00</t>
-  </si>
-  <si>
-    <t>14:24:00</t>
-  </si>
-  <si>
-    <t>12:23:00</t>
-  </si>
-  <si>
-    <t>11:55:00</t>
-  </si>
-  <si>
-    <t>08:50:00</t>
-  </si>
-  <si>
-    <t>3234890709 3234890709</t>
-  </si>
-  <si>
-    <t>3234895410 3234895410</t>
-  </si>
-  <si>
-    <t>3235101624 3235101624</t>
-  </si>
-  <si>
-    <t>3235242300 3235242300</t>
-  </si>
-  <si>
-    <t>3235298516 3235298516</t>
-  </si>
-  <si>
-    <t>3235580631 3235580631</t>
+    <t>95 EKONOMY UNLEADED</t>
+  </si>
+  <si>
+    <t>11:01</t>
+  </si>
+  <si>
+    <t>08:58</t>
+  </si>
+  <si>
+    <t>12:01</t>
+  </si>
+  <si>
+    <t>09:16</t>
+  </si>
+  <si>
+    <t>12:29</t>
+  </si>
+  <si>
+    <t>15:15</t>
   </si>
   <si>
     <t>Общи литри по продукт / РАЙОН ОДЕСОС</t>
@@ -144,9 +129,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -240,10 +225,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -538,7 +523,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -547,17 +532,16 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -597,277 +581,256 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="3">
+        <v>46237</v>
+      </c>
+      <c r="B2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="3">
-        <v>46219</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>14</v>
-      </c>
-      <c r="C2" t="s">
-        <v>15</v>
       </c>
       <c r="D2" t="s">
         <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F2">
-        <v>20.714</v>
-      </c>
-      <c r="G2" t="s">
-        <v>22</v>
+        <v>31.969</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0.64</v>
       </c>
       <c r="H2">
-        <v>0.62</v>
+        <v>20.46</v>
       </c>
       <c r="I2" s="1">
-        <v>12.843</v>
+        <v>0.65</v>
       </c>
       <c r="J2">
-        <v>0.63</v>
-      </c>
-      <c r="K2" s="1">
-        <v>13.05</v>
-      </c>
-      <c r="L2" t="s">
-        <v>23</v>
+        <v>20.78</v>
+      </c>
+      <c r="K2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L2">
+        <v>46070</v>
       </c>
       <c r="M2">
-        <v>59128</v>
-      </c>
-      <c r="N2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+        <v>241620</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="3">
-        <v>46219</v>
+        <v>46239</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
         <v>19</v>
       </c>
       <c r="E3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F3">
-        <v>28.127</v>
-      </c>
-      <c r="G3" t="s">
-        <v>22</v>
+        <v>28.121</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0.65</v>
       </c>
       <c r="H3">
-        <v>0.62</v>
+        <v>18.279</v>
       </c>
       <c r="I3" s="1">
-        <v>17.439</v>
+        <v>0.66</v>
       </c>
       <c r="J3">
-        <v>0.63</v>
-      </c>
-      <c r="K3" s="1">
-        <v>17.72</v>
-      </c>
-      <c r="L3" t="s">
-        <v>24</v>
+        <v>18.56</v>
+      </c>
+      <c r="K3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L3">
+        <v>59445</v>
       </c>
       <c r="M3">
-        <v>65338</v>
-      </c>
-      <c r="N3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+        <v>242385</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="3">
-        <v>46223</v>
+        <v>46241</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D4" t="s">
         <v>20</v>
       </c>
       <c r="E4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4">
+        <v>45.148</v>
+      </c>
+      <c r="G4" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="H4">
+        <v>68.625</v>
+      </c>
+      <c r="I4" s="1">
+        <v>1.55</v>
+      </c>
+      <c r="J4">
+        <v>69.979</v>
+      </c>
+      <c r="K4" t="s">
+        <v>26</v>
+      </c>
+      <c r="L4">
+        <v>215261</v>
+      </c>
+      <c r="M4">
+        <v>243575</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="3">
+        <v>46244</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" t="s">
         <v>21</v>
       </c>
-      <c r="F4">
-        <v>25.953</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="E5" t="s">
         <v>22</v>
       </c>
-      <c r="H4">
-        <v>0.63</v>
-      </c>
-      <c r="I4" s="1">
-        <v>16.35</v>
-      </c>
-      <c r="J4">
-        <v>0.64</v>
-      </c>
-      <c r="K4" s="1">
-        <v>16.61</v>
-      </c>
-      <c r="L4" t="s">
-        <v>25</v>
-      </c>
-      <c r="M4">
-        <v>862</v>
-      </c>
-      <c r="N4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" s="3">
-        <v>46226</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="F5">
+        <v>31.424</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="H5">
+        <v>20.426</v>
+      </c>
+      <c r="I5" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="J5">
+        <v>20.74</v>
+      </c>
+      <c r="K5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L5">
+        <v>65820</v>
+      </c>
+      <c r="M5">
+        <v>244938</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="3">
+        <v>46248</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
         <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5">
-        <v>25.594</v>
-      </c>
-      <c r="G5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H5">
-        <v>0.63</v>
-      </c>
-      <c r="I5" s="1">
-        <v>16.124</v>
-      </c>
-      <c r="J5">
-        <v>0.64</v>
-      </c>
-      <c r="K5" s="1">
-        <v>16.38</v>
-      </c>
-      <c r="L5" t="s">
-        <v>26</v>
-      </c>
-      <c r="M5">
-        <v>65471</v>
-      </c>
-      <c r="N5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="3">
-        <v>46227</v>
-      </c>
-      <c r="B6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" t="s">
-        <v>15</v>
       </c>
       <c r="D6" t="s">
         <v>18</v>
       </c>
       <c r="E6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F6">
-        <v>20.594</v>
-      </c>
-      <c r="G6" t="s">
-        <v>22</v>
+        <v>29.106</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0.65</v>
       </c>
       <c r="H6">
-        <v>0.63</v>
+        <v>18.919</v>
       </c>
       <c r="I6" s="1">
-        <v>12.974</v>
+        <v>0.66</v>
       </c>
       <c r="J6">
-        <v>0.64</v>
-      </c>
-      <c r="K6" s="1">
-        <v>13.18</v>
-      </c>
-      <c r="L6" t="s">
-        <v>27</v>
+        <v>19.21</v>
+      </c>
+      <c r="K6" t="s">
+        <v>28</v>
+      </c>
+      <c r="L6">
+        <v>46220</v>
       </c>
       <c r="M6">
-        <v>59270</v>
-      </c>
-      <c r="N6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+        <v>246753</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" s="3">
-        <v>46233</v>
+        <v>46248</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D7" t="s">
         <v>19</v>
       </c>
       <c r="E7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F7">
-        <v>23.359</v>
-      </c>
-      <c r="G7" t="s">
-        <v>22</v>
+        <v>25.015</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0.65</v>
       </c>
       <c r="H7">
-        <v>0.63</v>
+        <v>16.26</v>
       </c>
       <c r="I7" s="1">
-        <v>14.716</v>
+        <v>0.66</v>
       </c>
       <c r="J7">
-        <v>0.64</v>
-      </c>
-      <c r="K7" s="1">
-        <v>14.95</v>
-      </c>
-      <c r="L7" t="s">
-        <v>28</v>
+        <v>16.51</v>
+      </c>
+      <c r="K7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L7">
+        <v>59597</v>
       </c>
       <c r="M7">
-        <v>65636</v>
-      </c>
-      <c r="N7" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+        <v>246854</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10" s="4" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -875,62 +838,82 @@
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:13">
       <c r="A11" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
       <c r="A12" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" s="7">
-        <v>144.341</v>
-      </c>
-      <c r="C12" s="8">
+        <v>145.635</v>
+      </c>
+      <c r="C12" s="7">
+        <v>5</v>
+      </c>
+      <c r="D12" s="8">
+        <v>0.64781</v>
+      </c>
+      <c r="E12" s="7">
+        <v>94.34</v>
+      </c>
+      <c r="F12" s="7">
+        <v>95.8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="7">
+        <v>45.148</v>
+      </c>
+      <c r="C13" s="7">
+        <v>1</v>
+      </c>
+      <c r="D13" s="8">
+        <v>1.52</v>
+      </c>
+      <c r="E13" s="7">
+        <v>68.62</v>
+      </c>
+      <c r="F13" s="7">
+        <v>69.979</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="A14" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="10">
+        <v>190.783</v>
+      </c>
+      <c r="C14" s="10">
         <v>6</v>
       </c>
-      <c r="D12" s="8">
-        <v>0.627</v>
-      </c>
-      <c r="E12" s="8">
-        <v>90.446</v>
-      </c>
-      <c r="F12" s="8">
-        <v>91.89</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="A13" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="B13" s="10">
-        <v>144.341</v>
-      </c>
-      <c r="C13" s="10">
-        <v>6</v>
-      </c>
-      <c r="D13" s="8"/>
-      <c r="E13" s="10">
-        <v>90.446</v>
-      </c>
-      <c r="F13" s="10">
-        <v>91.89</v>
+      <c r="D14" s="8"/>
+      <c r="E14" s="10">
+        <v>162.96</v>
+      </c>
+      <c r="F14" s="10">
+        <v>165.779</v>
       </c>
     </row>
   </sheetData>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ОДЕСОС/РАЙОН ОДЕСОС.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ОДЕСОС/РАЙОН ОДЕСОС.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="38">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -55,7 +58,13 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>Варна Порт</t>
+    <t>1148 Варна пристанище</t>
+  </si>
+  <si>
+    <t>1146 Варна Сливница</t>
+  </si>
+  <si>
+    <t>B8984BP</t>
   </si>
   <si>
     <t>B7235BP</t>
@@ -64,10 +73,7 @@
     <t>B0593BT</t>
   </si>
   <si>
-    <t>B5779KH</t>
-  </si>
-  <si>
-    <t>B8984BP</t>
+    <t>78970155027722051</t>
   </si>
   <si>
     <t>78970155027722044</t>
@@ -76,34 +82,34 @@
     <t>78970155027722036</t>
   </si>
   <si>
-    <t>78970155027722028</t>
-  </si>
-  <si>
-    <t>78970155027722051</t>
-  </si>
-  <si>
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>95 EKONOMY UNLEADED</t>
-  </si>
-  <si>
-    <t>11:01</t>
-  </si>
-  <si>
-    <t>08:58</t>
-  </si>
-  <si>
-    <t>12:01</t>
-  </si>
-  <si>
-    <t>09:16</t>
-  </si>
-  <si>
-    <t>12:29</t>
-  </si>
-  <si>
-    <t>15:15</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>08:38:00</t>
+  </si>
+  <si>
+    <t>17:09:00</t>
+  </si>
+  <si>
+    <t>09:18:00</t>
+  </si>
+  <si>
+    <t>10:55:00</t>
+  </si>
+  <si>
+    <t>3236603846 3236603846</t>
+  </si>
+  <si>
+    <t>3236971558 3236971558</t>
+  </si>
+  <si>
+    <t>3236985212 3236985212</t>
+  </si>
+  <si>
+    <t>3236985248 3236985248</t>
   </si>
   <si>
     <t>Общи литри по продукт / РАЙОН ОДЕСОС</t>
@@ -128,10 +134,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00"/>
+    <numFmt numFmtId="167" formatCode="#,##0.00000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -211,7 +218,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -225,10 +232,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -523,7 +532,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -532,16 +541,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -581,57 +591,63 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
-        <v>46237</v>
+        <v>46253</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E2" t="s">
         <v>22</v>
       </c>
       <c r="F2">
-        <v>31.969</v>
-      </c>
-      <c r="G2" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="H2">
-        <v>20.46</v>
+        <v>26.27</v>
+      </c>
+      <c r="G2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H2" s="1">
+        <v>0.99</v>
       </c>
       <c r="I2" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="J2">
-        <v>20.78</v>
-      </c>
-      <c r="K2" t="s">
+        <v>26.007</v>
+      </c>
+      <c r="J2" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="K2" s="1">
+        <v>17.338</v>
+      </c>
+      <c r="L2" t="s">
         <v>24</v>
       </c>
-      <c r="L2">
-        <v>46070</v>
-      </c>
       <c r="M2">
-        <v>241620</v>
+        <v>65990</v>
+      </c>
+      <c r="N2" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:14">
       <c r="A3" s="3">
-        <v>46239</v>
+        <v>46260</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
         <v>19</v>
@@ -640,80 +656,86 @@
         <v>22</v>
       </c>
       <c r="F3">
-        <v>28.121</v>
-      </c>
-      <c r="G3" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="H3">
-        <v>18.279</v>
+        <v>24.09</v>
+      </c>
+      <c r="G3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="1">
+        <v>0.99</v>
       </c>
       <c r="I3" s="1">
+        <v>23.849</v>
+      </c>
+      <c r="J3" s="1">
         <v>0.66</v>
       </c>
-      <c r="J3">
-        <v>18.56</v>
-      </c>
-      <c r="K3" t="s">
+      <c r="K3" s="1">
+        <v>15.899</v>
+      </c>
+      <c r="L3" t="s">
         <v>25</v>
       </c>
-      <c r="L3">
-        <v>59445</v>
-      </c>
       <c r="M3">
-        <v>242385</v>
+        <v>66140</v>
+      </c>
+      <c r="N3" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:14">
       <c r="A4" s="3">
-        <v>46241</v>
+        <v>46261</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D4" t="s">
         <v>20</v>
       </c>
       <c r="E4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4">
+        <v>21.61</v>
+      </c>
+      <c r="G4" t="s">
         <v>23</v>
       </c>
-      <c r="F4">
-        <v>45.148</v>
-      </c>
-      <c r="G4" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="H4">
-        <v>68.625</v>
+      <c r="H4" s="1">
+        <v>0.99</v>
       </c>
       <c r="I4" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="J4">
-        <v>69.979</v>
-      </c>
-      <c r="K4" t="s">
+        <v>21.394</v>
+      </c>
+      <c r="J4" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="K4" s="1">
+        <v>14.263</v>
+      </c>
+      <c r="L4" t="s">
         <v>26</v>
       </c>
-      <c r="L4">
-        <v>215261</v>
-      </c>
       <c r="M4">
-        <v>243575</v>
+        <v>46340</v>
+      </c>
+      <c r="N4" t="s">
+        <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:14">
       <c r="A5" s="3">
-        <v>46244</v>
+        <v>46261</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D5" t="s">
         <v>21</v>
@@ -722,203 +744,104 @@
         <v>22</v>
       </c>
       <c r="F5">
-        <v>31.424</v>
-      </c>
-      <c r="G5" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="H5">
-        <v>20.426</v>
+        <v>31.76</v>
+      </c>
+      <c r="G5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" s="1">
+        <v>0.99</v>
       </c>
       <c r="I5" s="1">
+        <v>31.442</v>
+      </c>
+      <c r="J5" s="1">
         <v>0.66</v>
       </c>
-      <c r="J5">
-        <v>20.74</v>
-      </c>
-      <c r="K5" t="s">
+      <c r="K5" s="1">
+        <v>20.962</v>
+      </c>
+      <c r="L5" t="s">
         <v>27</v>
       </c>
-      <c r="L5">
-        <v>65820</v>
-      </c>
       <c r="M5">
-        <v>244938</v>
+        <v>59779</v>
+      </c>
+      <c r="N5" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="3">
-        <v>46248</v>
-      </c>
-      <c r="B6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" t="s">
+    <row r="8" spans="1:14">
+      <c r="A8" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="F6">
-        <v>29.106</v>
-      </c>
-      <c r="G6" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="H6">
-        <v>18.919</v>
-      </c>
-      <c r="I6" s="1">
-        <v>0.66</v>
-      </c>
-      <c r="J6">
-        <v>19.21</v>
-      </c>
-      <c r="K6" t="s">
-        <v>28</v>
-      </c>
-      <c r="L6">
-        <v>46220</v>
-      </c>
-      <c r="M6">
-        <v>246753</v>
+      <c r="B10" s="7">
+        <v>103.73</v>
+      </c>
+      <c r="C10" s="8">
+        <v>4</v>
+      </c>
+      <c r="D10" s="9">
+        <v>0.98999</v>
+      </c>
+      <c r="E10" s="7">
+        <v>102.69</v>
+      </c>
+      <c r="F10" s="7">
+        <v>68.45999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="3">
-        <v>46248</v>
-      </c>
-      <c r="B7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7">
-        <v>25.015</v>
-      </c>
-      <c r="G7" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="H7">
-        <v>16.26</v>
-      </c>
-      <c r="I7" s="1">
-        <v>0.66</v>
-      </c>
-      <c r="J7">
-        <v>16.51</v>
-      </c>
-      <c r="K7" t="s">
-        <v>29</v>
-      </c>
-      <c r="L7">
-        <v>59597</v>
-      </c>
-      <c r="M7">
-        <v>246854</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="A12" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" s="7">
-        <v>145.635</v>
-      </c>
-      <c r="C12" s="7">
-        <v>5</v>
-      </c>
-      <c r="D12" s="8">
-        <v>0.64781</v>
-      </c>
-      <c r="E12" s="7">
-        <v>94.34</v>
-      </c>
-      <c r="F12" s="7">
-        <v>95.8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
-      <c r="A13" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" s="7">
-        <v>45.148</v>
-      </c>
-      <c r="C13" s="7">
-        <v>1</v>
-      </c>
-      <c r="D13" s="8">
-        <v>1.52</v>
-      </c>
-      <c r="E13" s="7">
-        <v>68.62</v>
-      </c>
-      <c r="F13" s="7">
-        <v>69.979</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
-      <c r="A14" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="B14" s="10">
-        <v>190.783</v>
-      </c>
-      <c r="C14" s="10">
-        <v>6</v>
-      </c>
-      <c r="D14" s="8"/>
-      <c r="E14" s="10">
-        <v>162.96</v>
-      </c>
-      <c r="F14" s="10">
-        <v>165.779</v>
+    <row r="11" spans="1:14">
+      <c r="A11" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" s="11">
+        <v>103.73</v>
+      </c>
+      <c r="C11" s="12">
+        <v>4</v>
+      </c>
+      <c r="D11" s="9"/>
+      <c r="E11" s="11">
+        <v>102.69</v>
+      </c>
+      <c r="F11" s="11">
+        <v>68.45999999999999</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A8:F8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ОДЕСОС/РАЙОН ОДЕСОС.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ОДЕСОС/РАЙОН ОДЕСОС.xlsx
@@ -618,10 +618,10 @@
         <v>23</v>
       </c>
       <c r="H2" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I2" s="1">
-        <v>26.007</v>
+        <v>17.076</v>
       </c>
       <c r="J2" s="1">
         <v>0.66</v>
@@ -662,10 +662,10 @@
         <v>23</v>
       </c>
       <c r="H3" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I3" s="1">
-        <v>23.849</v>
+        <v>15.658</v>
       </c>
       <c r="J3" s="1">
         <v>0.66</v>
@@ -706,10 +706,10 @@
         <v>23</v>
       </c>
       <c r="H4" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I4" s="1">
-        <v>21.394</v>
+        <v>14.046</v>
       </c>
       <c r="J4" s="1">
         <v>0.66</v>
@@ -750,10 +750,10 @@
         <v>23</v>
       </c>
       <c r="H5" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I5" s="1">
-        <v>31.442</v>
+        <v>20.644</v>
       </c>
       <c r="J5" s="1">
         <v>0.66</v>
@@ -812,10 +812,10 @@
         <v>4</v>
       </c>
       <c r="D10" s="9">
-        <v>0.98999</v>
+        <v>0.65</v>
       </c>
       <c r="E10" s="7">
-        <v>102.69</v>
+        <v>67.42</v>
       </c>
       <c r="F10" s="7">
         <v>68.45999999999999</v>
@@ -833,7 +833,7 @@
       </c>
       <c r="D11" s="9"/>
       <c r="E11" s="11">
-        <v>102.69</v>
+        <v>67.42</v>
       </c>
       <c r="F11" s="11">
         <v>68.45999999999999</v>
